--- a/UAT_Excel_Reports/Promo Threshold_UAT.xlsx
+++ b/UAT_Excel_Reports/Promo Threshold_UAT.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -496,39 +496,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>D.1</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Navigate to the 'Create Promotions' page by entering the provided URL in the browser.</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>`page.goto("https://stage.mkr.esp.antuit.ai/nglcp/promotions/create-promotions")`</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>--- NAVIGATION TO PROMOTIONS PAGE ---</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>E.1</t>
+          <t>D.1</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Event Name' input field to focus on it.</t>
+          <t>Navigate to the 'Create Promotions' page by entering the provided URL in the browser.</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("promotionEventName").click()`</t>
+          <t>`page.goto("https://stage.mkr.esp.antuit.ai/nglcp/promotions/create-promotions")`</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr"/>
@@ -536,39 +523,26 @@
       <c r="F4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>E.2</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Enter the value 'rh--1220--0904' into the 'Event Name' input field.</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_test_id("promotionEventName").fill("rh--1220--0904")`</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>--- EVENT DETAILS INPUT ---</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>E.3</t>
+          <t>E.1</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Event Description' input field to focus on it.</t>
+          <t>Click on the 'Event Name' input field to focus on it.</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("promotionEventDescription").click()`</t>
+          <t>`page.get_by_test_id("promotionEventName").click()`</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr"/>
@@ -578,17 +552,17 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>E.4</t>
+          <t>E.2</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Enter the value 'PROMO THRESHOLD' into the 'Event Description' input field.</t>
+          <t>Enter the value 'rh--1220--0904' into the 'Event Name' input field.</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("promotionEventDescription").fill("PROMO THRESHOLD")`</t>
+          <t>`page.get_by_test_id("promotionEventName").fill("rh--1220--0904")`</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr"/>
@@ -598,17 +572,17 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>F.1</t>
+          <t>E.3</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Start Date' input field to open the date picker.</t>
+          <t>Click on the 'Event Description' input field to focus on it.</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("startDate").click()`</t>
+          <t>`page.get_by_test_id("promotionEventDescription").click()`</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr"/>
@@ -618,17 +592,17 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>F.2</t>
+          <t>E.4</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>From the date picker, select the 10th day of the month as the start date.</t>
+          <t>Enter the value 'PROMO THRESHOLD' into the 'Event Description' input field.</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("10", exact=True).click()`</t>
+          <t>`page.get_by_test_id("promotionEventDescription").fill("PROMO THRESHOLD")`</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr"/>
@@ -636,39 +610,26 @@
       <c r="F9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>F.3</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'End Date' input field to open the date picker.</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_test_id("endDate").click()`</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>--- DATE SELECTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>F.4</t>
+          <t>F.1</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>From the date picker, select the 17th day of the month as the end date.</t>
+          <t>Click on the 'Start Date' input field to open the date picker.</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("17").click()`</t>
+          <t>`page.get_by_test_id("startDate").click()`</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
@@ -678,17 +639,17 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>G.1</t>
+          <t>F.2</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'ASAP Pricing' checkbox to enable or disable this option.</t>
+          <t>From the date picker, select the 10th day of the month as the start date.</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("isAsapPricing").click()`</t>
+          <t>`page.get_by_text("10", exact=True).click()`</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr"/>
@@ -698,17 +659,17 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>G.2</t>
+          <t>F.3</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Click on the first tier in the 'Zebra Tiers' section to select it.</t>
+          <t>Click on the 'End Date' input field to open the date picker.</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>`page.locator(".zeb-tiers").first.click()`</t>
+          <t>`page.get_by_test_id("endDate").click()`</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -718,17 +679,17 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>H.1</t>
+          <t>F.4</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Hierarchy' option in the 'Location' filter section to expand the hierarchy options.</t>
+          <t>From the date picker, select the 17th day of the month as the end date.</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#SideFilterlocationhierarchyId").get_by_text("Hierarchy").click()`</t>
+          <t>`page.get_by_text("17").click()`</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr"/>
@@ -736,39 +697,26 @@
       <c r="F14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>H.2</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Select the 'Region' option from the expanded hierarchy options.</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Region", exact=True).click()`</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>--- ASAP PRICING AND ZEBRA TIERS ---</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>H.3</t>
+          <t>G.1</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Check the radio button for the 'NA' region to filter by this region.</t>
+          <t>Click on the 'ASAP Pricing' checkbox to enable or disable this option.</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("radio", name="NA", exact=True).check()`</t>
+          <t>`page.get_by_test_id("isAsapPricing").click()`</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr"/>
@@ -778,17 +726,17 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>H.4</t>
+          <t>G.2</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Price Zone Type' to expand the available price zone type options.</t>
+          <t>Click on the first tier in the 'Zebra Tiers' section to select it.</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Price Zone Type").click()`</t>
+          <t>`page.locator(".zeb-tiers").first.click()`</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr"/>
@@ -796,39 +744,26 @@
       <c r="F17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>H.5</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Select the 'Collection' option under 'Price Zone Type' to filter by this type.</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Collection$")).click()`</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>--- LOCATION FILTERS ---</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>H.6</t>
+          <t>H.1</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Price Zone' to expand the available price zone options.</t>
+          <t>Click on the 'Hierarchy' option in the 'Location' filter section to expand the hierarchy options.</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Price Zone", exact=True).click()`</t>
+          <t>`page.locator("#SideFilterlocationhierarchyId").get_by_text("Hierarchy").click()`</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr"/>
@@ -838,17 +773,17 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>H.7</t>
+          <t>H.2</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Select the '1_US Collection' option under 'Price Zone' to apply this specific filter.</t>
+          <t>Select the 'Region' option from the expanded hierarchy options.</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("1_US Collection").click()`</t>
+          <t>`page.get_by_text("Region", exact=True).click()`</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr"/>
@@ -858,17 +793,17 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>H.8</t>
+          <t>H.3</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply Filters' button to apply the selected location filters.</t>
+          <t>Check the radio button for the 'NA' region to filter by this region.</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Apply Filters").click()`</t>
+          <t>`page.get_by_role("radio", name="NA", exact=True).check()`</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr"/>
@@ -878,17 +813,17 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>I.1</t>
+          <t>H.4</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Select Products' textbox to open the product filter options.</t>
+          <t>Click on 'Price Zone Type' to expand the available price zone type options.</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("textbox", name="Select Products").click()`</t>
+          <t>`page.get_by_text("Price Zone Type").click()`</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr"/>
@@ -898,17 +833,17 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>I.2</t>
+          <t>H.5</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Hierarchy' option in the product filter section to expand the hierarchy options.</t>
+          <t>Select the 'Collection' option under 'Price Zone Type' to filter by this type.</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#SideFilterproducthierarchyId").get_by_text("Hierarchy").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Collection$")).click()`</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr"/>
@@ -918,17 +853,17 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>I.3</t>
+          <t>H.6</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Style Color' option from the expanded hierarchy options.</t>
+          <t>Click on 'Price Zone' to expand the available price zone options.</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Style Color").click()`</t>
+          <t>`page.get_by_text("Price Zone", exact=True).click()`</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr"/>
@@ -938,17 +873,17 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>I.4</t>
+          <t>H.7</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for 'Select All' under the 'Style Color' filter to select all available options.</t>
+          <t>Select the '1_US Collection' option under 'Price Zone' to apply this specific filter.</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(5) &gt; esp-filter-sub-accordion-v1 &gt; .sub-accordion-element &gt; .fiter-values-container &gt; .filter-options &gt; .filter-values-options &gt; .filter-values.d-flex.align-items-center.p-l-32.p-r-12 &gt; .custom-checkbox-wrapper").click()`</t>
+          <t>`page.get_by_text("1_US Collection").click()`</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr"/>
@@ -958,17 +893,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>I.5</t>
+          <t>H.8</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Check the checkbox for the specific product option 'C281-019999' under the 'Style Color' filter.</t>
+          <t>Click on the 'Apply Filters' button to apply the selected location filters.</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div:nth-child(5) &gt; esp-filter-sub-accordion-v1 &gt; .sub-accordion-element &gt; .fiter-values-container &gt; .filter-options &gt; .filter-values-options &gt; div:nth-child(2) &gt; .custom-checkbox-wrapper &gt; .pointer").click()`</t>
+          <t>`page.get_by_role("button", name="Apply Filters").click()`</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr"/>
@@ -976,39 +911,26 @@
       <c r="F26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>I.6</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Check the checkbox for the specific product option '004AHK003490' under the 'Style Color' filter.</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".pointer.custom-checkbox-unchecked").first.click()`</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>--- PRODUCT FILTERS ---</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>I.7</t>
+          <t>I.1</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply Filters' button to apply the selected product filters.</t>
+          <t>Click on the 'Select Products' textbox to open the product filter options.</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Apply Filters").click()`</t>
+          <t>`page.get_by_role("textbox", name="Select Products").click()`</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr"/>
@@ -1018,17 +940,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>J.1</t>
+          <t>I.2</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown for 'Optimization Objective' to view the available options.</t>
+          <t>Click on the 'Hierarchy' option in the product filter section to expand the hierarchy options.</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#optimizationObjective &gt; .multiselect-dropdown &gt; div &gt; .w-100").click()`</t>
+          <t>`page.locator("#SideFilterproducthierarchyId").get_by_text("Hierarchy").click()`</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr"/>
@@ -1038,17 +960,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>J.2</t>
+          <t>I.3</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Optimize for Sales Unit' option from the 'Optimization Objective' dropdown.</t>
+          <t>Select the 'Style Color' option from the expanded hierarchy options.</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("div").filter(has_text=re.compile(r"^Optimize for Sales Unit$")).nth(1).click()`</t>
+          <t>`page.get_by_text("Style Color").click()`</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr"/>
@@ -1058,17 +980,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>K.1</t>
+          <t>I.4</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Next Promo Recommendations' button to proceed to the next step in the promotion creation process.</t>
+          <t>Check the checkbox for 'Select All' under the 'Style Color' filter to select all available options.</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
+          <t>`page.locator("div:nth-child(5) &gt; esp-filter-sub-accordion-v1 &gt; .sub-accordion-element &gt; .fiter-values-container &gt; .filter-options &gt; .filter-values-options &gt; .filter-values.d-flex.align-items-center.p-l-32.p-r-12 &gt; .custom-checkbox-wrapper").click()`</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr"/>
@@ -1078,17 +1000,17 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>K.2</t>
+          <t>I.5</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Available Products' to view the list of products available for promotion.</t>
+          <t>Check the checkbox for the specific product option 'C281-019999' under the 'Style Color' filter.</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Available Products").click()`</t>
+          <t>`page.locator("div:nth-child(5) &gt; esp-filter-sub-accordion-v1 &gt; .sub-accordion-element &gt; .fiter-values-container &gt; .filter-options &gt; .filter-values-options &gt; div:nth-child(2) &gt; .custom-checkbox-wrapper &gt; .pointer").click()`</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr"/>
@@ -1098,17 +1020,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>K.3</t>
+          <t>I.6</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Show More' to expand the list of available products.</t>
+          <t>Check the checkbox for the specific product option '004AHK003490' under the 'Style Color' filter.</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Show More").click()`</t>
+          <t>`page.locator(".pointer.custom-checkbox-unchecked").first.click()`</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr"/>
@@ -1118,17 +1040,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>K.4</t>
+          <t>I.7</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Next' button to proceed to the promotion setup step.</t>
+          <t>Click on the 'Apply Filters' button to apply the selected product filters.</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
+          <t>`page.get_by_role("button", name="Apply Filters").click()`</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr"/>
@@ -1136,39 +1058,26 @@
       <c r="F34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>L.1</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Select the first option in the dropdown or list for promotion type by clicking on it.</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".w-100.p-h-16").first.click()`</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>--- OPTIMIZATION OBJECTIVE ---</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>L.2</t>
+          <t>J.1</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Bundle' option to select it as the promotion type.</t>
+          <t>Click on the dropdown for 'Optimization Objective' to view the available options.</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Bundle").click()`</t>
+          <t>`page.locator("#optimizationObjective &gt; .multiselect-dropdown &gt; div &gt; .w-100").click()`</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr"/>
@@ -1178,17 +1087,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>L.3</t>
+          <t>J.2</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Threshold' option to select it as an additional promotion type.</t>
+          <t>Select the 'Optimize for Sales Unit' option from the 'Optimization Objective' dropdown.</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Threshold").click()`</t>
+          <t>`page.locator("div").filter(has_text=re.compile(r"^Optimize for Sales Unit$")).nth(1).click()`</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr"/>
@@ -1196,39 +1105,26 @@
       <c r="F37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>M.1</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Click on the first checkbox to enable stacking rules or constraints.</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>--- PROMO RECOMMENDATIONS ---</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>M.2</t>
+          <t>K.1</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Click on the dropdown to specify the type of promotions to compare, with a maximum limit of 5.</t>
+          <t>Click on the 'Next Promo Recommendations' button to proceed to the next step in the promotion creation process.</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("What type of promotion(s) would you like to compare? *Max limit 5Promo Type").click()`</t>
+          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr"/>
@@ -1238,17 +1134,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>M.3</t>
+          <t>K.2</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Spend Amount' field to input the spending threshold for the promotion.</t>
+          <t>Click on 'Available Products' to view the list of products available for promotion.</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("spend_amount").click()`</t>
+          <t>`page.get_by_text("Available Products").click()`</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr"/>
@@ -1258,17 +1154,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>M.4</t>
+          <t>K.3</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Enter '5000' as the spending threshold for the promotion.</t>
+          <t>Click on 'Show More' to expand the list of available products.</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("spend_amount").fill("5000")`</t>
+          <t>`page.get_by_text("Show More").click()`</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr"/>
@@ -1278,17 +1174,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>M.5</t>
+          <t>K.4</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Get' field to input the discount percentage or value.</t>
+          <t>Click on the 'Next' button to proceed to the promotion setup step.</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>`page.locator("#get").click()`</t>
+          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr"/>
@@ -1296,39 +1192,26 @@
       <c r="F42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>M.6</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Enter '25' as the discount percentage or value for the promotion.</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>`page.locator("#get").fill("25")`</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>--- PROMOTION TYPE SELECTION ---</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>N.1</t>
+          <t>L.1</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Next' button to proceed to the next step in the promotion creation process.</t>
+          <t>Select the first option in the dropdown or list for promotion type by clicking on it.</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
+          <t>`page.locator(".w-100.p-h-16").first.click()`</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr"/>
@@ -1338,17 +1221,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>N.2</t>
+          <t>L.2</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Click on 'Price Zone Adjustment' to navigate to the price zone adjustment section.</t>
+          <t>Click on the 'Bundle' option to select it as the promotion type.</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Price Zone Adjustment").click()`</t>
+          <t>`page.get_by_text("Bundle").click()`</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr"/>
@@ -1358,17 +1241,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>N.3</t>
+          <t>L.3</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Apply' button to replicate the promotion details to sub-levels.</t>
+          <t>Click on the 'Threshold' option to select it as an additional promotion type.</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("replicate-apply").click()`</t>
+          <t>`page.get_by_text("Threshold").click()`</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr"/>
@@ -1376,39 +1259,26 @@
       <c r="F46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>O.1</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Navigate to the 'Product Details' page by entering the specified URL in the browser.</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>`page.goto("https://stage.mkr.esp.antuit.ai/nglcp/product-level-details/product-details")`</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="4" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr"/>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>--- PROMOTION RULES AND SPEND THRESHOLD ---</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>P.1</t>
+          <t>M.1</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Close' button to dismiss the current modal or overlay.</t>
+          <t>Click on the first checkbox to enable stacking rules or constraints.</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Close").click()`</t>
+          <t>`page.locator(".d-flex.flex-column.justify-content-center.font-size-10.align-items-center.checkbox-v2.m-r-10.zeb-check").first.click()`</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr"/>
@@ -1418,17 +1288,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>P.2</t>
+          <t>M.2</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Click on the 'Submit All for Approval' button to initiate the approval process for the selected scenario.</t>
+          <t>Click on the dropdown to specify the type of promotions to compare, with a maximum limit of 5.</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("submit-all-for-approval").click()`</t>
+          <t>`page.get_by_text("What type of promotion(s) would you like to compare? *Max limit 5Promo Type").click()`</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr"/>
@@ -1438,17 +1308,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>P.3</t>
+          <t>M.3</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Confirm the submission by clicking the 'Yes, Submit' button in the confirmation modal.</t>
+          <t>Click on the 'Spend Amount' field to input the spending threshold for the promotion.</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
+          <t>`page.get_by_test_id("spend_amount").click()`</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr"/>
@@ -1458,17 +1328,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>P.4</t>
+          <t>M.4</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Open the 'Actions' dropdown menu to access further options for the scenario.</t>
+          <t>Enter '5000' as the spending threshold for the promotion.</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Actions").click()`</t>
+          <t>`page.get_by_test_id("spend_amount").fill("5000")`</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr"/>
@@ -1478,17 +1348,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>P.5</t>
+          <t>M.5</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Approve' option from the dropdown to approve the scenario.</t>
+          <t>Click on the 'Get' field to input the discount percentage or value.</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Approve", exact=True).click()`</t>
+          <t>`page.locator("#get").click()`</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr"/>
@@ -1498,17 +1368,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>P.6</t>
+          <t>M.6</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Confirm the approval action by clicking the 'Confirm' button in the modal.</t>
+          <t>Enter '25' as the discount percentage or value for the promotion.</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
+          <t>`page.locator("#get").fill("25")`</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr"/>
@@ -1516,39 +1386,26 @@
       <c r="F53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>P.7</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Reopen the 'Actions' dropdown menu to access additional options.</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_role("button", name="Actions").click()`</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr"/>
-      <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr"/>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>--- PRICE ZONE ADJUSTMENT ---</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>P.8</t>
+          <t>N.1</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Select the 'Reject' option from the dropdown to reject the scenario.</t>
+          <t>Click on the 'Next' button to proceed to the next step in the promotion creation process.</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_text("Reject").click()`</t>
+          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr"/>
@@ -1558,17 +1415,17 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>P.9</t>
+          <t>N.2</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Confirm the rejection action by clicking the 'Confirm' button in the modal.</t>
+          <t>Click on 'Price Zone Adjustment' to navigate to the price zone adjustment section.</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
+          <t>`page.get_by_text("Price Zone Adjustment").click()`</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr"/>
@@ -1578,17 +1435,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>P.10</t>
+          <t>N.3</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Reopen the 'Actions' dropdown menu to access further options.</t>
+          <t>Click on the 'Apply' button to replicate the promotion details to sub-levels.</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_role("button", name="Actions").click()`</t>
+          <t>`page.get_by_test_id("replicate-apply").click()`</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr"/>
@@ -1596,39 +1453,26 @@
       <c r="F57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>P.11</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>Select the 'Withdraw' option from the dropdown to withdraw the scenario.</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_text("Withdraw", exact=True).click()`</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr"/>
-      <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>--- PRODUCT DETAILS NAVIGATION ---</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>P.12</t>
+          <t>O.1</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Confirm the withdrawal action by clicking the 'Confirm' button in the modal.</t>
+          <t>Navigate to the 'Product Details' page by entering the specified URL in the browser.</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
+          <t>`page.goto("https://stage.mkr.esp.antuit.ai/nglcp/product-level-details/product-details")`</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr"/>
@@ -1636,39 +1480,26 @@
       <c r="F59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>Q.1</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>Click on the 'Next' button to proceed to the next step in the promotion creation process.</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr"/>
-      <c r="E60" s="4" t="inlineStr"/>
-      <c r="F60" s="4" t="inlineStr"/>
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>--- APPROVAL WORKFLOW ---</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>Q.2</t>
+          <t>P.1</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Close the current page to complete the cleanup process.</t>
+          <t>Click on the 'Close' button to dismiss the current modal or overlay.</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>`page.close()`</t>
+          <t>`page.get_by_role("button", name="Close").click()`</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr"/>
@@ -1678,17 +1509,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Q.3</t>
+          <t>P.2</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Close the browser context to clean up resources associated with it.</t>
+          <t>Click on the 'Submit All for Approval' button to initiate the approval process for the selected scenario.</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>`context.close()`</t>
+          <t>`page.get_by_test_id("submit-all-for-approval").click()`</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr"/>
@@ -1698,26 +1529,307 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Q.4</t>
+          <t>P.3</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Close the browser instance to terminate the session completely.</t>
+          <t>Confirm the submission by clicking the 'Yes, Submit' button in the confirmation modal.</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>`browser.close()`</t>
+          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr"/>
       <c r="E63" s="4" t="inlineStr"/>
       <c r="F63" s="4" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>P.4</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Open the 'Actions' dropdown menu to access further options for the scenario.</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("button", name="Actions").click()`</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="4" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>P.5</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Select the 'Approve' option from the dropdown to approve the scenario.</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Approve", exact=True).click()`</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>P.6</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Confirm the approval action by clicking the 'Confirm' button in the modal.</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="4" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>P.7</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Reopen the 'Actions' dropdown menu to access additional options.</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("button", name="Actions").click()`</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr"/>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>P.8</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Select the 'Reject' option from the dropdown to reject the scenario.</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Reject").click()`</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr"/>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>P.9</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Confirm the rejection action by clicking the 'Confirm' button in the modal.</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr"/>
+      <c r="E69" s="4" t="inlineStr"/>
+      <c r="F69" s="4" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>P.10</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Reopen the 'Actions' dropdown menu to access further options.</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_role("button", name="Actions").click()`</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="4" t="inlineStr"/>
+      <c r="F70" s="4" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>P.11</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Select the 'Withdraw' option from the dropdown to withdraw the scenario.</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_text("Withdraw", exact=True).click()`</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr"/>
+      <c r="F71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>P.12</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Confirm the withdrawal action by clicking the 'Confirm' button in the modal.</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("confirm-modal-confirm-yes-button").click()`</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr"/>
+      <c r="F72" s="4" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>--- FINAL STEPS AND CLEANUP ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Q.1</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Click on the 'Next' button to proceed to the next step in the promotion creation process.</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>`page.get_by_test_id("create-promotions-next-button").click()`</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr"/>
+      <c r="E74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Q.2</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Close the current page to complete the cleanup process.</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>`page.close()`</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr"/>
+      <c r="E75" s="4" t="inlineStr"/>
+      <c r="F75" s="4" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Q.3</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Close the browser context to clean up resources associated with it.</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>`context.close()`</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr"/>
+      <c r="E76" s="4" t="inlineStr"/>
+      <c r="F76" s="4" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Q.4</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Close the browser instance to terminate the session completely.</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>`browser.close()`</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr"/>
+      <c r="F77" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="15">
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A43:F43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
